--- a/data_raw/educando_para_conservar/kobo_mensual_raw.xlsx
+++ b/data_raw/educando_para_conservar/kobo_mensual_raw.xlsx
@@ -7,7 +7,11 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Educando para Conservar - Re..." sheetId="1" r:id="rId1"/>
+    <sheet name="rep_centro" sheetId="2" r:id="rId2"/>
+    <sheet name="rep_campo" sheetId="3" r:id="rId3"/>
+    <sheet name="rep_diplomado_operativo" sheetId="4" r:id="rId4"/>
+    <sheet name="rep_coordinacion" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,6 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -44,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -340,9 +348,1738 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:BR2"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>deviceid</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>programa_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>programa_nombre</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>intro</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>anio_reportado</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>nota_anio</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>mes_reportado</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>mes_num</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>estado_reporte</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>periodo_clave</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>observaciones_generales</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>modulos_activos</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>modulos_activos/cobertura</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>modulos_activos/campo</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>modulos_activos/diplomado</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>modulos_activos/coordinacion</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>nota_modulos</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>nota_cobertura</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>centros_reportados_mes</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>docentes_nuevos_mes</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>estudiantes_nuevos_epc_mes</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>resumen_cobertura</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>nota_campo</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>actividades_campo_ejecutadas_mes</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>estudiantes_nuevos_campo_mes</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>resumen_campo</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>nota_diplomado_operativo</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>nota_diplomado_oficial</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>jovenes_formados_total_corte</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>propuestas_juveniles_total_corte</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>capitales_semilla_total_corte</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>resumen_diplomado_oficial</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>nota_coordinacion</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>coordinaciones_mes</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>resumen_coordinacion</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>meta_anual_docentes_capacitados</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>meta_anual_centros_cobertura</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>meta_anual_estudiantes_epc</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>meta_anual_estudiantes_campo</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>meta_anual_actividades_campo</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>meta_anual_reforestacion</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>meta_anual_monitoreo_reforestacion</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>meta_anual_tul</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>meta_anual_ferias</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>meta_anual_huertos</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>meta_anual_giras</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>meta_anual_murales</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>meta_anual_centros_acopio</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>meta_anual_limpieza_escolar</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>meta_anual_proyectos_gestion</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>meta_anual_jovenes_formados</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>meta_anual_propuestas_juveniles</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>meta_anual_capitales_semilla</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>nota_revision_1</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>nota_revision_2</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>comentarios_revision</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>_id</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>_uuid</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>_submission_time</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>_validation_status</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>_notes</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>_status</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>_submitted_by</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>__version__</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>_tags</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>meta/rootUuid</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>_index</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>46094.34767438658</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46094.34938006944</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46093</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ee.kobotoolbox.org:U6VBRZrqozC5JwCT</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>educando_para_conservar</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Educando para Conservar</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>feb</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>final_validado</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-feb</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>cobertura campo diplomado coordinacion</t>
+        </is>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>3514</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>3514</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BH2">
+        <v>695920316</v>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>12c85567-68d1-4955-b8d2-1d681ffc7200</t>
+        </is>
+      </c>
+      <c r="BJ2" s="1">
+        <v>46094.599375</v>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>vcX49nAkSbyozEnmU2XpoC</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>uuid:12c85567-68d1-4955-b8d2-1d681ffc7200</t>
+        </is>
+      </c>
+      <c r="BR2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AS2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_centro</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>municipio_centro</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>centro_educativo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>niveles_centro</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>niveles_centro/primaria_segundo_ciclo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>niveles_centro/basico</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>niveles_centro/diversificado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>acciones_centro</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>acciones_centro/taller_induccion</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>acciones_centro/seguimiento_epc</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>acciones_centro/diagnostico_inicial</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>acciones_centro/entrega_material</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>acciones_centro/sesion_pedagogica</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>acciones_centro/socializacion_campo</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>acciones_centro/otro</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>temas_epc</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>temas_epc/gestion_ambiental</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>temas_epc/residuos_solidos</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>temas_epc/agua_saneamiento</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>temas_epc/bosque_reforestacion</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>temas_epc/biodiversidad</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>temas_epc/cambio_climatico</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>temas_epc/otro</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>docentes_atendidos</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>docentes_nuevos_capacitados</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>directores_participantes</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>materiales_entregados</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>estudiantes_diagnostico</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>estudiantes_atendidos_mes</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>estudiantes_nuevos_epc</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>evidencia_centro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>observaciones_centro</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>_index</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>_parent_table_name</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>_parent_index</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>_submission__id</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>_submission__uuid</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>_submission__submission_time</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>_submission__validation_status</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>_submission__notes</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>_submission__status</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>_submission__submitted_by</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>_submission___version__</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>_submission__tags</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>_submission_meta/rootUuid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>solola</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Panimatzalan</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>basico</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>seguimiento_epc</t>
+        </is>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>gestion_ambiental</t>
+        </is>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>34</v>
+      </c>
+      <c r="Y2">
+        <v>21</v>
+      </c>
+      <c r="Z2">
+        <v>34</v>
+      </c>
+      <c r="AA2">
+        <v>56</v>
+      </c>
+      <c r="AB2">
+        <v>32</v>
+      </c>
+      <c r="AC2">
+        <v>60</v>
+      </c>
+      <c r="AD2">
+        <v>34</v>
+      </c>
+      <c r="AG2">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Educando para Conservar - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="AI2">
+        <v>1</v>
+      </c>
+      <c r="AJ2">
+        <v>695920316</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>12c85567-68d1-4955-b8d2-1d681ffc7200</t>
+        </is>
+      </c>
+      <c r="AL2" s="1">
+        <v>46094.599375</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>vcX49nAkSbyozEnmU2XpoC</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>uuid:12c85567-68d1-4955-b8d2-1d681ffc7200</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_campo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>municipio_campo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>centro_campo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_actividad_campo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>estado_actividad_campo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>estudiantes_participantes_evento</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>estudiantes_nuevos_campo</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes_participantes_evento</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>lugar_actividad</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>resultado_actividad</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>evidencia_campo</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>observaciones_campo</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>actividad_campo_ejecutada_flag</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>_index</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>_parent_table_name</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>_parent_index</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>_submission__id</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>_submission__uuid</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>_submission__submission_time</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>_submission__validation_status</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>_submission__notes</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>_submission__status</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>_submission__submitted_by</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>_submission___version__</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>_submission__tags</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>_submission_meta/rootUuid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>solola</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tzala</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>mural_pedagogico</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ejecutada</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Educando para Conservar - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>695920316</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>12c85567-68d1-4955-b8d2-1d681ffc7200</t>
+        </is>
+      </c>
+      <c r="S2" s="1">
+        <v>46094.599375</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>vcX49nAkSbyozEnmU2XpoC</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>uuid:12c85567-68d1-4955-b8d2-1d681ffc7200</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AI2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_diplomado_operativo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>cohorte_operativa</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/solola</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/san_jose_chacaya</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/santa_lucia_utatlan</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/panajachel</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/santa_catarina_palopo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/san_antonio_palopo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/san_andres_semetabaj</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/santiago_atitlan</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/san_lucas_toliman</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/san_juan_la_laguna</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/san_pablo_la_laguna</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/santa_cruz_la_laguna</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/san_marcos_la_laguna</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>municipios_diplomado_operativo/otro_fuera_lista</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>tipo_movimiento_diplomado</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>jovenes_alcanzados_operativo</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>avance_diplomado_operativo</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>evidencia_diplomado_operativo</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>observaciones_diplomado_operativo</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>_index</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>_parent_table_name</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>_parent_index</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>_submission__id</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>_submission__uuid</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>_submission__submission_time</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>_submission__validation_status</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>_submission__notes</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>_submission__status</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>_submission__submitted_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>_submission___version__</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>_submission__tags</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>_submission_meta/rootUuid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cohorte_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>solola santa_lucia_utatlan panajachel</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>modulo_formativo</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>60</v>
+      </c>
+      <c r="W2">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Educando para Conservar - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2">
+        <v>695920316</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>12c85567-68d1-4955-b8d2-1d681ffc7200</t>
+        </is>
+      </c>
+      <c r="AB2" s="1">
+        <v>46094.599375</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>vcX49nAkSbyozEnmU2XpoC</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>uuid:12c85567-68d1-4955-b8d2-1d681ffc7200</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AH2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_coordinacion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/solola</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/san_jose_chacaya</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/santa_lucia_utatlan</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/panajachel</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/santa_catarina_palopo</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/san_antonio_palopo</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/san_andres_semetabaj</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/santiago_atitlan</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/san_lucas_toliman</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/san_juan_la_laguna</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/san_pablo_la_laguna</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/santa_cruz_la_laguna</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/san_marcos_la_laguna</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>municipios_coordinacion/otro_fuera_lista</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>tipo_coordinacion</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>instituciones_coordinacion</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>resultado_coordinacion</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>evidencia_coordinacion</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>observaciones_coordinacion</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>_index</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>_parent_table_name</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>_parent_index</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>_submission__id</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>_submission__uuid</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>_submission__submission_time</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>_submission__validation_status</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>_submission__notes</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>_submission__status</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>_submission__submitted_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>_submission___version__</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>_submission__tags</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>_submission_meta/rootUuid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>panajachel</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>reunion_equipo</t>
+        </is>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Educando para Conservar - Reporte mensual único 2026</t>
+        </is>
+      </c>
+      <c r="X2">
+        <v>1</v>
+      </c>
+      <c r="Y2">
+        <v>695920316</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12c85567-68d1-4955-b8d2-1d681ffc7200</t>
+        </is>
+      </c>
+      <c r="AA2" s="1">
+        <v>46094.599375</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>submitted_via_web</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>vcX49nAkSbyozEnmU2XpoC</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>uuid:12c85567-68d1-4955-b8d2-1d681ffc7200</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>